--- a/chatbot/knowledge_base/mice-finance-kb.xlsx
+++ b/chatbot/knowledge_base/mice-finance-kb.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -811,36 +811,408 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Apakah Mice bisa memberi saran investasi atau nasihat keuangan?</t>
+          <t>Apakah data transaksi dan budget aku disimpan di mana?</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Mice fokus bantu kamu mencatat dan memahami arus keuangan kamu sendiri — bukan penasihat investasi atau pajak ya, kak. Buat keputusan investasi atau pajak, sebaiknya konsultasi ke ahlinya.</t>
+          <t>Semua transaksi dan budget kamu tersimpan otomatis di spreadsheet pribadi kamu, jadi kamu selalu bisa akses dan lihat langsung datanya kapan aja di luar chat sama Mice juga.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Apakah data transaksi dan budget aku disimpan di mana?</t>
+          <t>Kalau aku salah bilang jumlah transaksi, apa Mice bisa nolak nyatetnya?</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Semua transaksi dan budget kamu tersimpan otomatis di spreadsheet pribadi kamu, jadi kamu selalu bisa akses dan lihat langsung datanya kapan aja di luar chat sama Mice juga.</t>
+          <t>Mice nggak bisa tau kalau angkanya salah ketik ya kak, tapi begitu kamu sadar salah, tinggal bilang aja "transaksi tadi salah, harusnya segini" dan Mice bakal langsung koreksi.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Kalau aku salah bilang jumlah transaksi, apa Mice bisa nolak nyatetnya?</t>
+          <t>Apakah Mice bisa kasih saran investasi atau rekomendasi keuangan?</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mice nggak bisa tau kalau angkanya salah ketik ya kak, tapi begitu kamu sadar salah, tinggal bilang aja "transaksi tadi salah, harusnya segini" dan Mice bakal langsung koreksi.</t>
+          <t>Bisa, kak! Mice bisa kasih gambaran umum soal opsi keuangan kamu — misalnya sisa saldo cocoknya diapain, atau perbandingan instrumen kayak emas vs saham. Contoh: - "sisa saldo ku bisa buat apa aja?" - "dana 1jt mending beli emas atau beli saham?" - "aku punya 500rb, baiknya ditabung atau investasi?" Mice bakal kasih prinsip umum yang bisa kamu pertimbangkan, bukan rekomendasi produk spesifik ya.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Can Mice give investment advice or financial recommendations?</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Yes! Mice can give you general guidance on your finances — like what to do with your remaining balance, or comparing options like gold vs stocks. Examples: - "what can I do with my remaining balance?" - "should I invest 1 million in gold or stocks?" - "I have 500k, should I save it or invest it?" Mice gives general principles you can consider, not specific product recommendations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Kalau aku nanya saran keuangan tanpa nyebutin jumlah uangnya, gimana?</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Nggak masalah, kak! Kalau kamu nanya kayak "sisa saldo ku bisa buat apa aja?" tanpa sebutin angka, Mice bakal otomatis cek saldo kamu saat ini dulu, baru kasih saran berdasarkan jumlah itu. Kalau kamu udah sebutin jumlahnya sendiri (misal "dana 1jt mending diapain"), Mice langsung pakai angka itu tanpa perlu cek saldo lagi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>What happens if I ask for financial advice without mentioning an amount?</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>No worries! If you ask something like "what can I do with my remaining balance?" without a specific number, Mice will automatically check your current balance first, then base its suggestion on that amount. If you already stated an amount yourself (e.g. "what should I do with 1 million"), Mice uses that number directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Apakah saran keuangan dari Mice itu saran resmi dari penasihat keuangan?</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Bukan ya, kak. Saran dari Mice itu prinsip umum yang biasa dipakai (misal soal diversifikasi, dana darurat dulu sebelum investasi, sesuaikan sama jangka waktu kamu) — bukan nasihat keuangan personal dari penasihat berlisensi. Buat keputusan besar kayak investasi dalam jumlah besar, pinjaman, atau perencanaan pajak, tetap sebaiknya konsultasi ke ahlinya langsung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Is Mice's financial advice the same as advice from a licensed financial advisor?</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>No — Mice shares general, commonly-accepted principles (like diversification, building an emergency fund before investing, or matching your choices to your time horizon), not personalized advice from a licensed advisor. For major decisions like large investments, loans, or tax planning, it's best to consult a professional directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Instrumen keuangan apa aja yang bisa Mice bahas kalau aku minta saran?</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Mice bisa bahas kategori umum kayak: tabungan, deposito, emas, reksadana pasar uang, reksadana campuran, saham, dan obligasi — dijelasin plus-minusnya secara umum (likuiditas, risiko, cocok buat jangka waktu berapa lama). Mice nggak nyebutin nama produk, platform, atau saham spesifik ya, kak — itu di luar cakupan Mice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>What kind of financial instruments can Mice discuss if I ask for advice?</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Mice can discuss general categories like: savings, time deposits, gold, money market funds, mixed mutual funds, stocks, and bonds — explaining the general pros/cons (liquidity, risk, typical time horizon). Mice doesn't recommend specific products, platforms, or stock tickers — that's outside what Mice does.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Apa bedanya nanya 'saldo aku berapa' sama nanya 'sisa saldo ku buat apa aja'?</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Beda, kak! "Saldo aku berapa" itu Mice kasih tau ANGKA saldo kamu aja. Tapi "sisa saldo ku buat apa aja" itu Mice kasih SARAN soal gimana baiknya uang itu dipakai atau dialokasikan. Yang pertama laporan, yang kedua rekomendasi — dua-duanya bisa kamu tanya kapan aja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>What's the difference between asking 'what's my balance' and 'what can I do with my balance'?</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>They're different! "What's my balance" gives you the raw NUMBER. "What can I do with my balance" gives you a RECOMMENDATION on how to use or allocate that money. The first is a report, the second is guidance — you can ask either one anytime.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Kalau pertanyaan keuangan aku terlalu spesifik/personal (misal soal pinjaman KPR), Mice tetep bisa bantu?</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Mice tetep bisa kasih pertimbangan umum soal itu, kak, tapi buat keputusan besar dan personal kayak pinjaman KPR, ambil utang, atau perencanaan pajak, Mice bakal saranin kamu buat ngobrol sama penasihat keuangan berlisensi — soalnya itu butuh liat kondisi kamu secara lengkap yang Mice nggak punya aksesnya.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Can Mice help with a very specific/personal financial decision like a mortgage loan?</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Mice can still share general considerations, but for major personal decisions like mortgage loans, taking on debt, or tax planning, Mice will recommend speaking with a licensed financial advisor — those decisions need a full picture of your situation that Mice doesn't have access to.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Apa itu tabungan dan kapan cocok dipakai?</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Tabungan itu instrumen paling likuid, kak — uangnya bisa diambil kapan aja tanpa penalti, tapi bunganya kecil banget, kadang di bawah inflasi. Cocok buat dana darurat atau uang yang mungkin kamu butuh dalam waktu dekat (kurang dari setahun). Bukan pilihan buat numbuhin uang dalam jangka panjang.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>What is a savings account and when is it a good fit?</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>A savings account is the most liquid option — you can withdraw anytime with no penalty, but interest is very low, often below inflation. It's a good fit for an emergency fund or money you might need soon (under a year). It's not meant for long-term growth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Apa itu deposito dan gimana cara kerjanya?</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Deposito itu kamu nyimpen uang di bank buat jangka waktu tertentu (misal 1, 3, 6, atau 12 bulan) dengan bunga yang lebih tinggi dari tabungan biasa. Risikonya rendah, tapi uangnya nggak bisa diambil bebas sebelum jatuh tempo tanpa kena penalti. Cocok buat dana yang udah pasti nggak kepake dalam waktu dekat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>What is a time deposit and how does it work?</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>A time deposit means locking your money in a bank for a fixed period (e.g. 1, 3, 6, or 12 months) in exchange for a higher interest rate than a regular savings account. Risk is low, but you can't withdraw freely before maturity without a penalty. Good for funds you're sure you won't need soon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Apa itu investasi emas dan cocok buat siapa?</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Emas biasanya dipakai buat jaga nilai uang dalam jangka panjang (lindung nilai dari inflasi), bukan buat cuan cepat. Harganya cenderung stabil naik dalam jangka panjang tapi bisa fluktuatif jangka pendek. Likuiditasnya lumayan baik — bisa dijual relatif mudah. Cocok buat yang mau instrumen konservatif di luar uang tunai.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>What is gold investment and who is it suited for?</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Gold is usually used to preserve value over the long term (a hedge against inflation), not for quick gains. Prices tend to trend upward long-term but can fluctuate short-term. Liquidity is decent — it can be sold relatively easily. Good for people wanting a conservative option beyond cash.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Apa itu reksadana pasar uang?</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Reksadana pasar uang itu dana yang dikelola buat diinvestasikan ke instrumen jangka pendek yang risikonya rendah (kayak deposito dan obligasi jangka pendek). Risiko dan potensi return-nya lebih rendah dibanding jenis reksadana lain, tapi lebih likuid dan stabil. Sering jadi pilihan awal buat yang baru mulai investasi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>What is a money market fund?</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>A money market fund pools money to invest in low-risk, short-term instruments (like time deposits and short-term bonds). Risk and potential return are lower than other fund types, but it's more liquid and stable. Often a common starting point for new investors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Apa itu reksadana campuran?</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Reksadana campuran itu dana yang dikelola dengan kombinasi beberapa instrumen sekaligus — biasanya campuran saham, obligasi, dan pasar uang. Risiko dan potensi return-nya di tengah-tengah, lebih tinggi dari reksadana pasar uang tapi lebih rendah dari saham murni. Cocok buat yang mau diversifikasi tanpa milih sendiri-sendiri.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>What is a mixed/balanced mutual fund?</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>A mixed mutual fund invests across a combination of instruments — typically a mix of stocks, bonds, and money market instruments. Risk and potential return sit in the middle, higher than a money market fund but lower than pure stocks. Good for diversification without picking each instrument yourself.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Apa itu saham dan risikonya gimana?</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Saham itu kamu beli sebagian kecil kepemilikan sebuah perusahaan. Potensi returnnya paling tinggi dibanding instrumen lain dalam jangka panjang, tapi harganya juga paling fluktuatif — bisa naik atau turun signifikan dalam waktu singkat. Biasanya cocok buat dana yang jangka waktunya panjang (5 tahun ke atas) dan kamu udah siap sama risiko turunnya nilai.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>What are stocks and what's the risk like?</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Stocks mean buying a small ownership stake in a company. They have the highest long-term return potential among common instruments, but prices are also the most volatile — they can swing significantly in a short time. Usually best suited for money with a long time horizon (5+ years) where you're prepared for the value to drop temporarily.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Apa itu obligasi?</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Obligasi itu kayak kamu minjemin uang ke pemerintah atau perusahaan, dan sebagai gantinya kamu dapet bunga tetap secara berkala sampai jatuh tempo. Risikonya lebih rendah dari saham tapi lebih tinggi dari deposito, dan returnnya cenderung lebih stabil serta terprediksi. Cocok buat yang mau pendapatan tetap dengan risiko menengah.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>What are bonds?</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>A bond is essentially lending money to a government or company, and in return you receive fixed periodic interest until maturity. Risk is lower than stocks but higher than time deposits, and returns tend to be more stable and predictable. Good for those wanting steady income with moderate risk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Gimana cara Mice bantu aku milih instrumen yang cocok?</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Mice bakal nanya atau pertimbangin jangka waktu kamu (mau dipakai kapan) dan seberapa nyaman kamu sama risiko naik-turun nilai, baru kasih gambaran kategori instrumen yang biasanya cocok. Tapi keputusan akhir tetap di tangan kamu ya, kak — dan buat jumlah besar, tetap disaranin konsultasi ke penasihat keuangan berlisensi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>How does Mice help me choose the right instrument?</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Mice will consider (or ask about) your time horizon and how comfortable you are with value fluctuations, then give you a general picture of instrument categories that usually fit. The final decision is still yours — and for larger amounts, it's still recommended to consult a licensed financial advisor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Apa itu diversifikasi dan kenapa penting?</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Diversifikasi itu nyebar uang kamu ke beberapa instrumen berbeda, bukan naruh semuanya di satu tempat. Tujuannya biar kalau satu instrumen lagi turun nilainya, nggak semua uang kamu ikut turun sekaligus. Ini prinsip umum yang biasa dipakai buat ngurangin risiko, walau tetap nggak menghilangkan risiko sepenuhnya.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>What is diversification and why does it matter?</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Diversification means spreading your money across several different instruments instead of putting it all in one place. The goal is that if one instrument drops in value, not all your money drops at the same time. It's a general principle commonly used to reduce risk, though it doesn't eliminate risk entirely.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Kenapa Mice sering nyaranin dana darurat dulu sebelum investasi?</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Karena dana darurat itu jaring pengaman kalau ada kebutuhan mendadak (misal sakit atau kehilangan pekerjaan), kak. Kalau kamu langsung investasi semua uang tanpa dana darurat, kamu bisa kepaksa jual investasi di waktu yang kurang pas cuma buat nutup kebutuhan mendadak. Idealnya dana darurat itu setara 3-6 bulan pengeluaran, disimpan di instrumen yang likuid kayak tabungan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Why does Mice often suggest an emergency fund before investing?</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Because an emergency fund acts as a safety net for unexpected needs (like illness or job loss). If you invest everything without one, you might be forced to sell investments at a bad time just to cover an urgent expense. Ideally an emergency fund covers 3-6 months of expenses, kept in a liquid instrument like a savings account.</t>
         </is>
       </c>
     </row>
